--- a/bom-out-v0.2/示例文件/GP4.0F-引脚定义.xlsx
+++ b/bom-out-v0.2/示例文件/GP4.0F-引脚定义.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\bom-out-v0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="23745" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>接插件端口</t>
   </si>
@@ -64,7 +64,7 @@
     <t>●</t>
   </si>
   <si>
-    <t>U12</t>
+    <t>U12,U12_1</t>
   </si>
   <si>
     <t>F13</t>
@@ -73,13 +73,16 @@
     <t>电动尾翼电源</t>
   </si>
   <si>
+    <t>U12,U12_3</t>
+  </si>
+  <si>
     <t>D13</t>
   </si>
   <si>
     <t>左前门信号采集</t>
   </si>
   <si>
-    <t>U12,C12</t>
+    <t>U12,C12,U12_2</t>
   </si>
   <si>
     <t>F6</t>
@@ -97,7 +100,7 @@
     <t>右前门信号采集</t>
   </si>
   <si>
-    <t>C12,R13</t>
+    <t>C12,R13,U12_1</t>
   </si>
   <si>
     <t>A4</t>
@@ -106,22 +109,25 @@
     <t>右后门信号采集</t>
   </si>
   <si>
+    <t>R13,C12_2</t>
+  </si>
+  <si>
+    <t>F44</t>
+  </si>
+  <si>
+    <t>左前组合灯电源</t>
+  </si>
+  <si>
     <t>R13</t>
   </si>
   <si>
-    <t>F44</t>
-  </si>
-  <si>
-    <t>左前组合灯电源</t>
-  </si>
-  <si>
     <t>G43</t>
   </si>
   <si>
     <t>热管理集成模块电源</t>
   </si>
   <si>
-    <t>R12</t>
+    <t>R12,R12_1</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1288,7 @@
     <col min="2" max="2" width="22.125" customWidth="1"/>
     <col min="3" max="3" width="10.5083333333333" customWidth="1"/>
     <col min="5" max="5" width="10.3416666666667" customWidth="1"/>
-    <col min="6" max="6" width="11.5333333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1342,15 +1348,15 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:6">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -1362,15 +1368,15 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:6">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
@@ -1382,15 +1388,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -1402,15 +1408,15 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -1422,15 +1428,15 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
@@ -1442,15 +1448,15 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:6">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
@@ -1462,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
